--- a/case_studies/base_case/2025/technologies.xlsx
+++ b/case_studies/base_case/2025/technologies.xlsx
@@ -791,10 +791,10 @@
         <v>17.75</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>16.44</v>
+        <v>35.39</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>34.39</v>
+        <v>31.27</v>
       </c>
       <c r="L3" s="5" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="Z3" s="5" t="n">
-        <v>44.5</v>
+        <v>42.99</v>
       </c>
       <c r="AA3" s="5" t="n">
         <v>0</v>
@@ -885,13 +885,13 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>31.03</v>
+        <v>26.13</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>146.74</v>
+        <v>153.06</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>30.09</v>
+        <v>20.3</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>0</v>
@@ -936,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>38.94</v>
+        <v>27.91</v>
       </c>
       <c r="AA4" s="3" t="n">
         <v>0</v>
@@ -985,10 +985,10 @@
         <v>84.31999999999999</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>139.82</v>
+        <v>229.84</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>163.36</v>
+        <v>148.52</v>
       </c>
       <c r="L5" s="5" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="Z5" s="5" t="n">
-        <v>211.38</v>
+        <v>204.22</v>
       </c>
       <c r="AA5" s="5" t="n">
         <v>0</v>
